--- a/data/Ficha_12_DL1153_202605_GestantesReferidas.xlsx
+++ b/data/Ficha_12_DL1153_202605_GestantesReferidas.xlsx
@@ -16,17 +16,17 @@
     <sheet name="sheet1" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">sheet1!$A$1:$O$146</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">sheet1!$A$1:$O$162</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="90" r:id="rId3"/>
+    <pivotCache cacheId="100" r:id="rId3"/>
   </pivotCaches>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1223" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1351" uniqueCount="204">
   <si>
     <t>Mes</t>
   </si>
@@ -589,7 +589,55 @@
     <t>PERIODO: ENERO - MAYO 2026</t>
   </si>
   <si>
-    <t>FUENTE: HISMINSA: 17/05/2026 | Refcon: 11/05/2026</t>
+    <t>61999983</t>
+  </si>
+  <si>
+    <t>45085017</t>
+  </si>
+  <si>
+    <t>42963908</t>
+  </si>
+  <si>
+    <t>74602569</t>
+  </si>
+  <si>
+    <t>76809059</t>
+  </si>
+  <si>
+    <t>73849629</t>
+  </si>
+  <si>
+    <t>73956003</t>
+  </si>
+  <si>
+    <t>71205592</t>
+  </si>
+  <si>
+    <t>71248804</t>
+  </si>
+  <si>
+    <t>71177904</t>
+  </si>
+  <si>
+    <t>70121433</t>
+  </si>
+  <si>
+    <t>62088660</t>
+  </si>
+  <si>
+    <t>60354072</t>
+  </si>
+  <si>
+    <t>48136457</t>
+  </si>
+  <si>
+    <t>47028640</t>
+  </si>
+  <si>
+    <t>45145270</t>
+  </si>
+  <si>
+    <t>FUENTE: HISMINSA: 24/05/2026 | Refcon: 25/05/2026</t>
   </si>
 </sst>
 </file>
@@ -1022,7 +1070,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="TuSoft" refreshedDate="46160.521390393522" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="145">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="TuSoft" refreshedDate="46167.522919560186" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="161">
   <cacheSource type="worksheet">
     <worksheetSource name="Tabla1"/>
   </cacheSource>
@@ -1037,8 +1085,8 @@
         <n v="1"/>
         <n v="3"/>
         <n v="4"/>
+        <n v="5"/>
         <n v="2"/>
-        <n v="5"/>
       </sharedItems>
     </cacheField>
     <cacheField name="Departamento" numFmtId="0">
@@ -1087,7 +1135,7 @@
       <sharedItems/>
     </cacheField>
     <cacheField name="Fecha_Referencia" numFmtId="14">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-01-02T00:00:00" maxDate="2026-05-10T00:00:00"/>
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-01-02T00:00:00" maxDate="2026-05-25T00:00:00"/>
     </cacheField>
     <cacheField name="Den" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="1"/>
@@ -1096,7 +1144,7 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1"/>
     </cacheField>
     <cacheField name="CantAten" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="11"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="12"/>
     </cacheField>
     <cacheField name="Indicador" numFmtId="0" formula="Num/Den" databaseField="0"/>
   </cacheFields>
@@ -1109,7 +1157,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="145">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="161">
   <r>
     <x v="0"/>
     <x v="0"/>
@@ -1180,6 +1228,23 @@
   </r>
   <r>
     <x v="0"/>
+    <x v="3"/>
+    <s v="HUANCAVELICA"/>
+    <x v="0"/>
+    <s v="ACOBAMBA"/>
+    <x v="0"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="3917"/>
+    <s v="61999983"/>
+    <d v="2026-05-14T00:00:00"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
     <x v="0"/>
     <s v="HUANCAVELICA"/>
     <x v="0"/>
@@ -1197,7 +1262,24 @@
   </r>
   <r>
     <x v="0"/>
-    <x v="3"/>
+    <x v="0"/>
+    <s v="HUANCAVELICA"/>
+    <x v="0"/>
+    <s v="ACOBAMBA"/>
+    <x v="0"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="3917"/>
+    <s v="74769893"/>
+    <d v="2026-01-05T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="4"/>
     <s v="HUANCAVELICA"/>
     <x v="0"/>
     <s v="ACOBAMBA"/>
@@ -1231,7 +1313,7 @@
   </r>
   <r>
     <x v="0"/>
-    <x v="3"/>
+    <x v="4"/>
     <s v="HUANCAVELICA"/>
     <x v="0"/>
     <s v="ACOBAMBA"/>
@@ -1301,23 +1383,6 @@
     <x v="0"/>
     <x v="0"/>
     <s v="HUANCAVELICA"/>
-    <x v="0"/>
-    <s v="ACOBAMBA"/>
-    <x v="0"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="0"/>
-    <x v="0"/>
-    <n v="3917"/>
-    <s v="74769893"/>
-    <d v="2026-01-05T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="3"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="HUANCAVELICA"/>
     <x v="1"/>
     <s v="PAMPAS"/>
     <x v="1"/>
@@ -1333,7 +1398,7 @@
   </r>
   <r>
     <x v="0"/>
-    <x v="3"/>
+    <x v="4"/>
     <s v="HUANCAVELICA"/>
     <x v="1"/>
     <s v="PAMPAS"/>
@@ -1363,7 +1428,7 @@
     <d v="2026-04-15T00:00:00"/>
     <n v="1"/>
     <n v="1"/>
-    <n v="2"/>
+    <n v="3"/>
   </r>
   <r>
     <x v="0"/>
@@ -1384,6 +1449,23 @@
   </r>
   <r>
     <x v="0"/>
+    <x v="3"/>
+    <s v="HUANCAVELICA"/>
+    <x v="1"/>
+    <s v="PAMPAS"/>
+    <x v="1"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="4074"/>
+    <s v="45085017"/>
+    <d v="2026-05-15T00:00:00"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
     <x v="1"/>
     <s v="HUANCAVELICA"/>
     <x v="1"/>
@@ -1410,15 +1492,15 @@
     <x v="0"/>
     <x v="1"/>
     <n v="4074"/>
-    <s v="47605869"/>
-    <d v="2026-03-23T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="8"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="3"/>
+    <s v="73518403"/>
+    <d v="2026-03-25T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="4"/>
     <s v="HUANCAVELICA"/>
     <x v="1"/>
     <s v="PAMPAS"/>
@@ -1452,7 +1534,7 @@
   </r>
   <r>
     <x v="0"/>
-    <x v="3"/>
+    <x v="4"/>
     <s v="HUANCAVELICA"/>
     <x v="1"/>
     <s v="PAMPAS"/>
@@ -1495,6 +1577,23 @@
     <x v="0"/>
     <x v="1"/>
     <n v="4074"/>
+    <s v="47605869"/>
+    <d v="2026-03-23T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="HUANCAVELICA"/>
+    <x v="1"/>
+    <s v="PAMPAS"/>
+    <x v="1"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="4074"/>
     <s v="47791018"/>
     <d v="2026-03-31T00:00:00"/>
     <n v="1"/>
@@ -1503,7 +1602,7 @@
   </r>
   <r>
     <x v="0"/>
-    <x v="3"/>
+    <x v="4"/>
     <s v="HUANCAVELICA"/>
     <x v="1"/>
     <s v="PAMPAS"/>
@@ -1571,23 +1670,6 @@
   </r>
   <r>
     <x v="0"/>
-    <x v="1"/>
-    <s v="HUANCAVELICA"/>
-    <x v="1"/>
-    <s v="PAMPAS"/>
-    <x v="1"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="0"/>
-    <x v="1"/>
-    <n v="4074"/>
-    <s v="73518403"/>
-    <d v="2026-03-25T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="4"/>
-  </r>
-  <r>
-    <x v="0"/>
     <x v="2"/>
     <s v="HUANCAVELICA"/>
     <x v="2"/>
@@ -1622,7 +1704,7 @@
   </r>
   <r>
     <x v="0"/>
-    <x v="3"/>
+    <x v="4"/>
     <s v="HUANCAVELICA"/>
     <x v="2"/>
     <s v="HUANCAVELICA"/>
@@ -1639,6 +1721,23 @@
   </r>
   <r>
     <x v="0"/>
+    <x v="3"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="42963908"/>
+    <d v="2026-05-20T00:00:00"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
     <x v="0"/>
     <s v="HUANCAVELICA"/>
     <x v="2"/>
@@ -1656,7 +1755,7 @@
   </r>
   <r>
     <x v="0"/>
-    <x v="3"/>
+    <x v="4"/>
     <s v="HUANCAVELICA"/>
     <x v="2"/>
     <s v="HUANCAVELICA"/>
@@ -1682,6 +1781,2029 @@
     <x v="1"/>
     <x v="2"/>
     <n v="3853"/>
+    <s v="77049174"/>
+    <d v="2026-04-29T00:00:00"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="77134905"/>
+    <d v="2026-01-08T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="77462313"/>
+    <d v="2026-03-10T00:00:00"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="77600416"/>
+    <d v="2026-04-09T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="90404185"/>
+    <d v="2026-01-25T00:00:00"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="74602569"/>
+    <d v="2026-05-17T00:00:00"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="75226956"/>
+    <d v="2026-03-03T00:00:00"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="76081886"/>
+    <d v="2026-01-14T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="76127414"/>
+    <d v="2026-03-16T00:00:00"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="4"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="76370685"/>
+    <d v="2026-02-23T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="76809059"/>
+    <d v="2026-05-24T00:00:00"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="73956876"/>
+    <d v="2026-03-17T00:00:00"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="4"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="74127311"/>
+    <d v="2026-02-18T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="4"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="74228765"/>
+    <d v="2026-02-23T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="74393281"/>
+    <d v="2026-03-29T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="74454673"/>
+    <d v="2026-01-26T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="74565709"/>
+    <d v="2026-03-18T00:00:00"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="73524808"/>
+    <d v="2026-01-25T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="73558138"/>
+    <d v="2026-04-28T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="73741871"/>
+    <d v="2026-03-09T00:00:00"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="73849629"/>
+    <d v="2026-05-13T00:00:00"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="73955626"/>
+    <d v="2026-03-14T00:00:00"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="73956003"/>
+    <d v="2026-05-22T00:00:00"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="72270228"/>
+    <d v="2026-01-10T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="72275552"/>
+    <d v="2026-01-20T00:00:00"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="4"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="72848468"/>
+    <d v="2026-02-08T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="73014236"/>
+    <d v="2026-05-06T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="73138494"/>
+    <d v="2026-04-23T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="73441298"/>
+    <d v="2026-04-22T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="71564300"/>
+    <d v="2026-04-24T00:00:00"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="71875961"/>
+    <d v="2026-01-28T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="4"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="71913621"/>
+    <d v="2026-02-17T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="7"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="4"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="71943754"/>
+    <d v="2026-02-14T00:00:00"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="72240065"/>
+    <d v="2026-01-13T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="72240069"/>
+    <d v="2026-01-23T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="4"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="71390117"/>
+    <d v="2026-02-17T00:00:00"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="71400358"/>
+    <d v="2026-04-20T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="71408791"/>
+    <d v="2026-04-17T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="4"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="71410243"/>
+    <d v="2026-02-17T00:00:00"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="71519086"/>
+    <d v="2026-04-08T00:00:00"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="71529543"/>
+    <d v="2026-05-06T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="4"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="71375554"/>
+    <d v="2026-02-10T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="71377645"/>
+    <d v="2026-01-07T00:00:00"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="71378046"/>
+    <d v="2026-01-27T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="71383018"/>
+    <d v="2026-04-17T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="4"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="71384733"/>
+    <d v="2026-02-07T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="4"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="71384998"/>
+    <d v="2026-02-21T00:00:00"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="71260118"/>
+    <d v="2026-05-05T00:00:00"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="71277395"/>
+    <d v="2026-01-26T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="71278758"/>
+    <d v="2026-04-29T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="71296904"/>
+    <d v="2026-04-09T00:00:00"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="71372797"/>
+    <d v="2026-03-19T00:00:00"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="71373386"/>
+    <d v="2026-03-05T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="71200567"/>
+    <d v="2026-03-19T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="71205592"/>
+    <d v="2026-05-22T00:00:00"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="71235543"/>
+    <d v="2026-04-26T00:00:00"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="71236590"/>
+    <d v="2026-04-22T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="71248804"/>
+    <d v="2026-05-13T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="4"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="71253521"/>
+    <d v="2026-02-27T00:00:00"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="70354614"/>
+    <d v="2026-05-19T00:00:00"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="70789576"/>
+    <d v="2026-01-28T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="70873026"/>
+    <d v="2026-01-27T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="71009879"/>
+    <d v="2026-01-25T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="4"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="71079209"/>
+    <d v="2026-02-25T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="7"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="71177904"/>
+    <d v="2026-05-14T00:00:00"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="62667410"/>
+    <d v="2026-04-07T00:00:00"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="70092745"/>
+    <d v="2026-05-07T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="70092761"/>
+    <d v="2026-01-21T00:00:00"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="70121433"/>
+    <d v="2026-05-23T00:00:00"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="70158416"/>
+    <d v="2026-03-29T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="70329192"/>
+    <d v="2026-01-21T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="4"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="61688511"/>
+    <d v="2026-02-24T00:00:00"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="4"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="62006035"/>
+    <d v="2026-02-24T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="62068165"/>
+    <d v="2026-04-24T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="62088660"/>
+    <d v="2026-05-15T00:00:00"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="4"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="62101766"/>
+    <d v="2026-02-14T00:00:00"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="62520114"/>
+    <d v="2026-04-25T00:00:00"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="60901398"/>
+    <d v="2026-03-26T00:00:00"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="60901458"/>
+    <d v="2026-01-12T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="60901487"/>
+    <d v="2026-04-29T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="61028163"/>
+    <d v="2026-03-16T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="4"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="61132279"/>
+    <d v="2026-02-17T00:00:00"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="61307287"/>
+    <d v="2026-01-21T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="6"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="60354072"/>
+    <d v="2026-05-20T00:00:00"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="60390889"/>
+    <d v="2026-01-22T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="60508202"/>
+    <d v="2026-03-03T00:00:00"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="60544490"/>
+    <d v="2026-04-03T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="60660047"/>
+    <d v="2026-03-08T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="60824461"/>
+    <d v="2026-01-06T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="60092674"/>
+    <d v="2026-03-04T00:00:00"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="4"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="60254827"/>
+    <d v="2026-02-07T00:00:00"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="60259108"/>
+    <d v="2026-03-11T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="60278191"/>
+    <d v="2026-04-23T00:00:00"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="60313493"/>
+    <d v="2026-03-17T00:00:00"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="60322207"/>
+    <d v="2026-04-09T00:00:00"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="48265015"/>
+    <d v="2026-03-05T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="48378290"/>
+    <d v="2026-01-10T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="48512083"/>
+    <d v="2026-04-11T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="48651284"/>
+    <d v="2026-01-09T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="4"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="48974079"/>
+    <d v="2026-02-12T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="60091654"/>
+    <d v="2026-03-03T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="4"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="47432354"/>
+    <d v="2026-02-09T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="47511778"/>
+    <d v="2026-03-06T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="47533514"/>
+    <d v="2026-03-26T00:00:00"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="47837679"/>
+    <d v="2026-01-02T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="48046179"/>
+    <d v="2026-01-13T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="8"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="48136457"/>
+    <d v="2026-05-14T00:00:00"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="45511508"/>
+    <d v="2026-05-04T00:00:00"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="4"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="46080462"/>
+    <d v="2026-02-19T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="46952035"/>
+    <d v="2026-01-28T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="47028640"/>
+    <d v="2026-05-15T00:00:00"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="47270989"/>
+    <d v="2026-01-08T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="47316243"/>
+    <d v="2026-03-15T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="12"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="4"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="44387844"/>
+    <d v="2026-02-05T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="45047750"/>
+    <d v="2026-01-12T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="4"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="45073557"/>
+    <d v="2026-02-09T00:00:00"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="45145270"/>
+    <d v="2026-05-15T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="4"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="45262252"/>
+    <d v="2026-02-12T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
+    <s v="45372129"/>
+    <d v="2026-01-30T00:00:00"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="10"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="HUANCAVELICA"/>
+    <x v="2"/>
+    <s v="NO PERTENECE A NINGUNA MICRORED"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="3853"/>
     <s v="43343367"/>
     <d v="2026-04-13T00:00:00"/>
     <n v="1"/>
@@ -1690,1792 +3812,7 @@
   </r>
   <r>
     <x v="0"/>
-    <x v="1"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="77462313"/>
-    <d v="2026-03-10T00:00:00"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="77600416"/>
-    <d v="2026-04-09T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="90404185"/>
-    <d v="2026-01-25T00:00:00"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="1"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="75226956"/>
-    <d v="2026-03-03T00:00:00"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="76081886"/>
-    <d v="2026-01-14T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="5"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="1"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="76127414"/>
-    <d v="2026-03-16T00:00:00"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="0"/>
     <x v="3"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="76370685"/>
-    <d v="2026-02-23T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="6"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="77049174"/>
-    <d v="2026-04-29T00:00:00"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="77134905"/>
-    <d v="2026-01-08T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="5"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="1"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="73956876"/>
-    <d v="2026-03-17T00:00:00"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="3"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="74127311"/>
-    <d v="2026-02-18T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="3"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="74228765"/>
-    <d v="2026-02-23T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="6"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="1"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="74393281"/>
-    <d v="2026-03-29T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="5"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="74454673"/>
-    <d v="2026-01-26T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="5"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="1"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="74565709"/>
-    <d v="2026-03-18T00:00:00"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="73138494"/>
-    <d v="2026-04-23T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="73441298"/>
-    <d v="2026-04-22T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="4"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="73524808"/>
-    <d v="2026-01-25T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="4"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="73558138"/>
-    <d v="2026-04-28T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="1"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="73741871"/>
-    <d v="2026-03-09T00:00:00"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="1"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="73955626"/>
-    <d v="2026-03-14T00:00:00"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="72240065"/>
-    <d v="2026-01-13T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="72240069"/>
-    <d v="2026-01-23T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="5"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="72270228"/>
-    <d v="2026-01-10T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="72275552"/>
-    <d v="2026-01-20T00:00:00"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="3"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="72848468"/>
-    <d v="2026-02-08T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="3"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="4"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="73014236"/>
-    <d v="2026-05-06T00:00:00"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="71519086"/>
-    <d v="2026-04-08T00:00:00"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="4"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="71529543"/>
-    <d v="2026-05-06T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="3"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="71564300"/>
-    <d v="2026-04-24T00:00:00"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="71875961"/>
-    <d v="2026-01-28T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="3"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="3"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="71913621"/>
-    <d v="2026-02-17T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="7"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="3"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="71943754"/>
-    <d v="2026-02-14T00:00:00"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="3"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="71384733"/>
-    <d v="2026-02-07T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="4"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="3"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="71384998"/>
-    <d v="2026-02-21T00:00:00"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="3"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="71390117"/>
-    <d v="2026-02-17T00:00:00"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="71400358"/>
-    <d v="2026-04-20T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="3"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="71408791"/>
-    <d v="2026-04-17T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="3"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="71410243"/>
-    <d v="2026-02-17T00:00:00"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="1"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="71372797"/>
-    <d v="2026-03-19T00:00:00"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="1"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="71373386"/>
-    <d v="2026-03-05T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="5"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="3"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="71375554"/>
-    <d v="2026-02-10T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="4"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="71377645"/>
-    <d v="2026-01-07T00:00:00"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="71378046"/>
-    <d v="2026-01-27T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="71383018"/>
-    <d v="2026-04-17T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="3"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="71236590"/>
-    <d v="2026-04-22T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="3"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="3"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="71253521"/>
-    <d v="2026-02-27T00:00:00"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="4"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="71260118"/>
-    <d v="2026-05-05T00:00:00"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="71277395"/>
-    <d v="2026-01-26T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="5"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="71278758"/>
-    <d v="2026-04-29T00:00:00"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="71296904"/>
-    <d v="2026-04-09T00:00:00"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="70789576"/>
-    <d v="2026-01-28T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="70873026"/>
-    <d v="2026-01-27T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="3"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="71009879"/>
-    <d v="2026-01-25T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="3"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="3"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="71079209"/>
-    <d v="2026-02-25T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="7"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="1"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="71200567"/>
-    <d v="2026-03-19T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="5"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="71235543"/>
-    <d v="2026-04-26T00:00:00"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="62667410"/>
-    <d v="2026-04-07T00:00:00"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="4"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="70092745"/>
-    <d v="2026-05-07T00:00:00"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="70092761"/>
-    <d v="2026-01-21T00:00:00"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="1"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="70158416"/>
-    <d v="2026-03-29T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="70329192"/>
-    <d v="2026-01-21T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="3"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="4"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="70354614"/>
-    <d v="2026-05-09T00:00:00"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="61307287"/>
-    <d v="2026-01-21T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="6"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="3"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="61688511"/>
-    <d v="2026-02-24T00:00:00"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="3"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="62006035"/>
-    <d v="2026-02-24T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="3"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="62068165"/>
-    <d v="2026-04-24T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="3"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="62101766"/>
-    <d v="2026-02-14T00:00:00"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="62520114"/>
-    <d v="2026-04-25T00:00:00"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="60824461"/>
-    <d v="2026-01-06T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="3"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="1"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="60901398"/>
-    <d v="2026-03-26T00:00:00"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="60901458"/>
-    <d v="2026-01-12T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="4"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="60901487"/>
-    <d v="2026-04-29T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="1"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="61028163"/>
-    <d v="2026-03-16T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="4"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="3"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="61132279"/>
-    <d v="2026-02-17T00:00:00"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="1"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="60313493"/>
-    <d v="2026-03-17T00:00:00"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="60322207"/>
-    <d v="2026-04-09T00:00:00"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="60390889"/>
-    <d v="2026-01-22T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="3"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="1"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="60508202"/>
-    <d v="2026-03-03T00:00:00"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="60544490"/>
-    <d v="2026-04-03T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="4"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="1"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="60660047"/>
-    <d v="2026-03-08T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="3"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="3"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="48974079"/>
-    <d v="2026-02-12T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="5"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="1"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="60091654"/>
-    <d v="2026-03-03T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="1"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="60092674"/>
-    <d v="2026-03-04T00:00:00"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="3"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="60254827"/>
-    <d v="2026-02-07T00:00:00"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="1"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="60259108"/>
-    <d v="2026-03-11T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="3"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="60278191"/>
-    <d v="2026-04-23T00:00:00"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="47837679"/>
-    <d v="2026-01-02T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="48046179"/>
-    <d v="2026-01-13T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="8"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="1"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="48265015"/>
-    <d v="2026-03-05T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="48378290"/>
-    <d v="2026-01-10T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="3"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="48512083"/>
-    <d v="2026-04-11T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="4"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="48651284"/>
-    <d v="2026-01-09T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="4"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="46952035"/>
-    <d v="2026-01-28T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="4"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="47270989"/>
-    <d v="2026-01-08T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="2"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="1"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="47316243"/>
-    <d v="2026-03-15T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="11"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="3"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="47432354"/>
-    <d v="2026-02-09T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="4"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="1"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="47511778"/>
-    <d v="2026-03-06T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="3"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="1"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="47533514"/>
-    <d v="2026-03-26T00:00:00"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="45047750"/>
-    <d v="2026-01-12T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="5"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="3"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="45073557"/>
-    <d v="2026-02-09T00:00:00"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="3"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="45262252"/>
-    <d v="2026-02-12T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="3"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="0"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="45372129"/>
-    <d v="2026-01-30T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="10"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="4"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="45511508"/>
-    <d v="2026-05-04T00:00:00"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="3"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="46080462"/>
-    <d v="2026-02-19T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="3"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="4"/>
     <s v="HUANCAVELICA"/>
     <x v="2"/>
     <s v="HUANCAVELICA"/>
@@ -3505,7 +3842,7 @@
     <d v="2026-01-10T00:00:00"/>
     <n v="1"/>
     <n v="1"/>
-    <n v="8"/>
+    <n v="9"/>
   </r>
   <r>
     <x v="0"/>
@@ -3526,7 +3863,7 @@
   </r>
   <r>
     <x v="0"/>
-    <x v="3"/>
+    <x v="4"/>
     <s v="HUANCAVELICA"/>
     <x v="2"/>
     <s v="HUANCAVELICA"/>
@@ -3543,7 +3880,7 @@
   </r>
   <r>
     <x v="0"/>
-    <x v="3"/>
+    <x v="4"/>
     <s v="HUANCAVELICA"/>
     <x v="2"/>
     <s v="HUANCAVELICA"/>
@@ -3557,155 +3894,12 @@
     <n v="1"/>
     <n v="1"/>
     <n v="4"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="3"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="HUANCAVELICA"/>
-    <x v="2"/>
-    <s v="NO PERTENECE A NINGUNA MICRORED"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="3853"/>
-    <s v="44387844"/>
-    <d v="2026-02-05T00:00:00"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="3"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica10" cacheId="90" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
-  <location ref="K8:N14" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="3" colPageCount="1"/>
-  <pivotFields count="16">
-    <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0" defaultSubtotal="0">
-      <items count="1">
-        <item x="0"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
-      <items count="6">
-        <item x="0"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisPage" compact="0" outline="0" showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item m="1" x="3"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisPage" compact="0" outline="0" showAll="0">
-      <items count="5">
-        <item m="1" x="3"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" numFmtId="164" outline="0" showAll="0"/>
-    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
-    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField dataField="1" compact="0" outline="0" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-    <i i="2">
-      <x v="2"/>
-    </i>
-  </colItems>
-  <pageFields count="3">
-    <pageField fld="0" hier="-1"/>
-    <pageField fld="5" hier="-1"/>
-    <pageField fld="8" hier="-1"/>
-  </pageFields>
-  <dataFields count="3">
-    <dataField name="Suma de Den" fld="12" baseField="0" baseItem="0"/>
-    <dataField name="Suma de Num" fld="13" baseField="0" baseItem="0"/>
-    <dataField name="Suma de Indicador" fld="15" baseField="0" baseItem="0" numFmtId="165"/>
-  </dataFields>
-  <formats count="2">
-    <format dxfId="22">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="21">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleMedium13" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica9" cacheId="90" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica9" cacheId="100" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A8:G12" firstHeaderRow="0" firstDataRow="1" firstDataCol="4" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="16">
     <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0" defaultSubtotal="0">
@@ -3716,10 +3910,10 @@
     <pivotField axis="axisPage" compact="0" outline="0" showAll="0">
       <items count="6">
         <item x="0"/>
-        <item x="3"/>
+        <item x="4"/>
         <item x="1"/>
         <item x="2"/>
-        <item x="4"/>
+        <item x="3"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -3818,6 +4012,132 @@
     <dataField name="Suma de Indicador" fld="15" baseField="0" baseItem="0" numFmtId="165"/>
   </dataFields>
   <formats count="2">
+    <format dxfId="22">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="21">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleMedium13" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica10" cacheId="100" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="K8:N14" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="3" colPageCount="1"/>
+  <pivotFields count="16">
+    <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0" defaultSubtotal="0">
+      <items count="1">
+        <item x="0"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisPage" compact="0" outline="0" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item m="1" x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisPage" compact="0" outline="0" showAll="0">
+      <items count="5">
+        <item m="1" x="3"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="164" outline="0" showAll="0"/>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField dataField="1" compact="0" outline="0" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+  </colItems>
+  <pageFields count="3">
+    <pageField fld="0" hier="-1"/>
+    <pageField fld="5" hier="-1"/>
+    <pageField fld="8" hier="-1"/>
+  </pageFields>
+  <dataFields count="3">
+    <dataField name="Suma de Den" fld="12" baseField="0" baseItem="0"/>
+    <dataField name="Suma de Num" fld="13" baseField="0" baseItem="0"/>
+    <dataField name="Suma de Indicador" fld="15" baseField="0" baseItem="0" numFmtId="165"/>
+  </dataFields>
+  <formats count="2">
     <format dxfId="24">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
@@ -3847,8 +4167,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:O146" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
-  <autoFilter ref="A1:O146"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:O162" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
+  <autoFilter ref="A1:O162"/>
   <tableColumns count="15">
     <tableColumn id="2" name="Año" dataDxfId="18"/>
     <tableColumn id="1" name="Mes" dataDxfId="17"/>
@@ -4161,7 +4481,7 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>187</v>
+        <v>203</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -4291,13 +4611,13 @@
         <v>17</v>
       </c>
       <c r="E9" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F9" s="4">
         <v>8</v>
       </c>
       <c r="G9" s="5">
-        <v>0.66666666666666663</v>
+        <v>0.61538461538461542</v>
       </c>
       <c r="K9">
         <v>1</v>
@@ -4326,13 +4646,13 @@
         <v>47</v>
       </c>
       <c r="E10" s="4">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="F10" s="4">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="G10" s="5">
-        <v>0.58974358974358976</v>
+        <v>0.56488549618320616</v>
       </c>
       <c r="K10">
         <v>2</v>
@@ -4361,13 +4681,13 @@
         <v>17</v>
       </c>
       <c r="E11" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F11" s="4">
         <v>15</v>
       </c>
       <c r="G11" s="5">
-        <v>0.9375</v>
+        <v>0.88235294117647056</v>
       </c>
       <c r="K11">
         <v>3</v>
@@ -4387,13 +4707,13 @@
         <v>134</v>
       </c>
       <c r="E12" s="4">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="F12" s="4">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="G12" s="5">
-        <v>0.6344827586206897</v>
+        <v>0.60248447204968947</v>
       </c>
       <c r="K12">
         <v>4</v>
@@ -4402,10 +4722,10 @@
         <v>28</v>
       </c>
       <c r="M12" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N12" s="5">
-        <v>0.5357142857142857</v>
+        <v>0.5714285714285714</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
@@ -4413,13 +4733,13 @@
         <v>5</v>
       </c>
       <c r="L13" s="4">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="M13" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N13" s="5">
-        <v>0.14285714285714285</v>
+        <v>0.21739130434782608</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -4427,13 +4747,13 @@
         <v>134</v>
       </c>
       <c r="L14" s="4">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="M14" s="4">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="N14" s="5">
-        <v>0.6344827586206897</v>
+        <v>0.60248447204968947</v>
       </c>
     </row>
   </sheetData>
@@ -4446,7 +4766,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O146"/>
+  <dimension ref="A1:O162"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.77734375" bestFit="1" customWidth="1"/>
@@ -4702,7 +5022,7 @@
         <v>2026</v>
       </c>
       <c r="B6" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>14</v>
@@ -4729,19 +5049,19 @@
         <v>3917</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>22</v>
+        <v>187</v>
       </c>
       <c r="L6" s="13">
-        <v>46037</v>
+        <v>46156</v>
       </c>
       <c r="M6" s="1">
         <v>1</v>
       </c>
       <c r="N6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
@@ -4749,7 +5069,7 @@
         <v>2026</v>
       </c>
       <c r="B7" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>14</v>
@@ -4776,10 +5096,10 @@
         <v>3917</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L7" s="13">
-        <v>46062</v>
+        <v>46037</v>
       </c>
       <c r="M7" s="1">
         <v>1</v>
@@ -4788,7 +5108,7 @@
         <v>1</v>
       </c>
       <c r="O7" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
@@ -4796,7 +5116,7 @@
         <v>2026</v>
       </c>
       <c r="B8" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>14</v>
@@ -4823,19 +5143,19 @@
         <v>3917</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="L8" s="13">
-        <v>46093</v>
+        <v>46027</v>
       </c>
       <c r="M8" s="1">
         <v>1</v>
       </c>
       <c r="N8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
@@ -4870,10 +5190,10 @@
         <v>3917</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L9" s="13">
-        <v>46072</v>
+        <v>46062</v>
       </c>
       <c r="M9" s="1">
         <v>1</v>
@@ -4917,10 +5237,10 @@
         <v>3917</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="L10" s="13">
-        <v>46085</v>
+        <v>46093</v>
       </c>
       <c r="M10" s="1">
         <v>1</v>
@@ -4937,7 +5257,7 @@
         <v>2026</v>
       </c>
       <c r="B11" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>14</v>
@@ -4964,10 +5284,10 @@
         <v>3917</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="L11" s="13">
-        <v>46034</v>
+        <v>46072</v>
       </c>
       <c r="M11" s="1">
         <v>1</v>
@@ -4976,7 +5296,7 @@
         <v>1</v>
       </c>
       <c r="O11" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
@@ -5011,19 +5331,19 @@
         <v>3917</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L12" s="13">
-        <v>46091</v>
+        <v>46085</v>
       </c>
       <c r="M12" s="1">
         <v>1</v>
       </c>
       <c r="N12" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
@@ -5058,10 +5378,10 @@
         <v>3917</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L13" s="13">
-        <v>46027</v>
+        <v>46034</v>
       </c>
       <c r="M13" s="1">
         <v>1</v>
@@ -5070,7 +5390,7 @@
         <v>1</v>
       </c>
       <c r="O13" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
@@ -5078,19 +5398,19 @@
         <v>2026</v>
       </c>
       <c r="B14" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>16</v>
@@ -5099,16 +5419,16 @@
         <v>17</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="J14" s="1">
-        <v>4074</v>
+        <v>3917</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="L14" s="13">
-        <v>46044</v>
+        <v>46091</v>
       </c>
       <c r="M14" s="1">
         <v>1</v>
@@ -5125,7 +5445,7 @@
         <v>2026</v>
       </c>
       <c r="B15" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>14</v>
@@ -5152,10 +5472,10 @@
         <v>4074</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L15" s="13">
-        <v>46066</v>
+        <v>46044</v>
       </c>
       <c r="M15" s="1">
         <v>1</v>
@@ -5164,7 +5484,7 @@
         <v>1</v>
       </c>
       <c r="O15" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
@@ -5172,7 +5492,7 @@
         <v>2026</v>
       </c>
       <c r="B16" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>14</v>
@@ -5199,10 +5519,10 @@
         <v>4074</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>173</v>
+        <v>34</v>
       </c>
       <c r="L16" s="13">
-        <v>46127</v>
+        <v>46066</v>
       </c>
       <c r="M16" s="1">
         <v>1</v>
@@ -5211,7 +5531,7 @@
         <v>1</v>
       </c>
       <c r="O16" s="1">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
@@ -5219,7 +5539,7 @@
         <v>2026</v>
       </c>
       <c r="B17" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>14</v>
@@ -5246,10 +5566,10 @@
         <v>4074</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>35</v>
+        <v>173</v>
       </c>
       <c r="L17" s="13">
-        <v>46034</v>
+        <v>46127</v>
       </c>
       <c r="M17" s="1">
         <v>1</v>
@@ -5258,7 +5578,7 @@
         <v>1</v>
       </c>
       <c r="O17" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
@@ -5266,7 +5586,7 @@
         <v>2026</v>
       </c>
       <c r="B18" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>14</v>
@@ -5293,10 +5613,10 @@
         <v>4074</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L18" s="13">
-        <v>46099</v>
+        <v>46034</v>
       </c>
       <c r="M18" s="1">
         <v>1</v>
@@ -5313,7 +5633,7 @@
         <v>2026</v>
       </c>
       <c r="B19" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>14</v>
@@ -5340,19 +5660,19 @@
         <v>4074</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>149</v>
+        <v>188</v>
       </c>
       <c r="L19" s="13">
-        <v>46104</v>
+        <v>46157</v>
       </c>
       <c r="M19" s="1">
         <v>1</v>
       </c>
       <c r="N19" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O19" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
@@ -5360,7 +5680,7 @@
         <v>2026</v>
       </c>
       <c r="B20" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>14</v>
@@ -5387,10 +5707,10 @@
         <v>4074</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="L20" s="13">
-        <v>46078</v>
+        <v>46099</v>
       </c>
       <c r="M20" s="1">
         <v>1</v>
@@ -5399,7 +5719,7 @@
         <v>1</v>
       </c>
       <c r="O20" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
@@ -5407,7 +5727,7 @@
         <v>2026</v>
       </c>
       <c r="B21" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>14</v>
@@ -5434,10 +5754,10 @@
         <v>4074</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>174</v>
+        <v>43</v>
       </c>
       <c r="L21" s="13">
-        <v>46121</v>
+        <v>46106</v>
       </c>
       <c r="M21" s="1">
         <v>1</v>
@@ -5446,7 +5766,7 @@
         <v>1</v>
       </c>
       <c r="O21" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
@@ -5481,10 +5801,10 @@
         <v>4074</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L22" s="13">
-        <v>46079</v>
+        <v>46078</v>
       </c>
       <c r="M22" s="1">
         <v>1</v>
@@ -5501,7 +5821,7 @@
         <v>2026</v>
       </c>
       <c r="B23" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>14</v>
@@ -5528,10 +5848,10 @@
         <v>4074</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>39</v>
+        <v>174</v>
       </c>
       <c r="L23" s="13">
-        <v>46047</v>
+        <v>46121</v>
       </c>
       <c r="M23" s="1">
         <v>1</v>
@@ -5540,7 +5860,7 @@
         <v>1</v>
       </c>
       <c r="O23" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
@@ -5548,7 +5868,7 @@
         <v>2026</v>
       </c>
       <c r="B24" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>14</v>
@@ -5575,10 +5895,10 @@
         <v>4074</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="L24" s="13">
-        <v>46112</v>
+        <v>46079</v>
       </c>
       <c r="M24" s="1">
         <v>1</v>
@@ -5595,7 +5915,7 @@
         <v>2026</v>
       </c>
       <c r="B25" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>14</v>
@@ -5622,10 +5942,10 @@
         <v>4074</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L25" s="13">
-        <v>46075</v>
+        <v>46047</v>
       </c>
       <c r="M25" s="1">
         <v>1</v>
@@ -5634,7 +5954,7 @@
         <v>1</v>
       </c>
       <c r="O25" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
@@ -5642,7 +5962,7 @@
         <v>2026</v>
       </c>
       <c r="B26" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>14</v>
@@ -5669,10 +5989,10 @@
         <v>4074</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>40</v>
+        <v>149</v>
       </c>
       <c r="L26" s="13">
-        <v>46052</v>
+        <v>46104</v>
       </c>
       <c r="M26" s="1">
         <v>1</v>
@@ -5681,7 +6001,7 @@
         <v>1</v>
       </c>
       <c r="O26" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
@@ -5689,7 +6009,7 @@
         <v>2026</v>
       </c>
       <c r="B27" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>14</v>
@@ -5716,10 +6036,10 @@
         <v>4074</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="L27" s="13">
-        <v>46042</v>
+        <v>46112</v>
       </c>
       <c r="M27" s="1">
         <v>1</v>
@@ -5728,7 +6048,7 @@
         <v>1</v>
       </c>
       <c r="O27" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
@@ -5736,7 +6056,7 @@
         <v>2026</v>
       </c>
       <c r="B28" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>14</v>
@@ -5763,19 +6083,19 @@
         <v>4074</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="L28" s="13">
-        <v>46036</v>
+        <v>46075</v>
       </c>
       <c r="M28" s="1">
         <v>1</v>
       </c>
       <c r="N28" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O28" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
@@ -5783,7 +6103,7 @@
         <v>2026</v>
       </c>
       <c r="B29" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>14</v>
@@ -5810,10 +6130,10 @@
         <v>4074</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="L29" s="13">
-        <v>46106</v>
+        <v>46052</v>
       </c>
       <c r="M29" s="1">
         <v>1</v>
@@ -5822,7 +6142,7 @@
         <v>1</v>
       </c>
       <c r="O29" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
@@ -5830,46 +6150,46 @@
         <v>2026</v>
       </c>
       <c r="B30" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>16</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="J30" s="1">
-        <v>3853</v>
+        <v>4074</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>155</v>
+        <v>41</v>
       </c>
       <c r="L30" s="13">
-        <v>46121</v>
+        <v>46042</v>
       </c>
       <c r="M30" s="1">
         <v>1</v>
       </c>
       <c r="N30" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O30" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
@@ -5883,31 +6203,31 @@
         <v>14</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>16</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="J31" s="1">
-        <v>3853</v>
+        <v>4074</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="L31" s="13">
-        <v>46045</v>
+        <v>46036</v>
       </c>
       <c r="M31" s="1">
         <v>1</v>
@@ -5924,7 +6244,7 @@
         <v>2026</v>
       </c>
       <c r="B32" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>14</v>
@@ -5951,19 +6271,19 @@
         <v>3853</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>50</v>
+        <v>155</v>
       </c>
       <c r="L32" s="13">
-        <v>46066</v>
+        <v>46121</v>
       </c>
       <c r="M32" s="1">
         <v>1</v>
       </c>
       <c r="N32" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O32" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
@@ -5998,19 +6318,19 @@
         <v>3853</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L33" s="13">
-        <v>46049</v>
+        <v>46045</v>
       </c>
       <c r="M33" s="1">
         <v>1</v>
       </c>
       <c r="N33" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O33" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
@@ -6045,19 +6365,19 @@
         <v>3853</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="L34" s="13">
-        <v>46076</v>
+        <v>46066</v>
       </c>
       <c r="M34" s="1">
         <v>1</v>
       </c>
       <c r="N34" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O34" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
@@ -6065,7 +6385,7 @@
         <v>2026</v>
       </c>
       <c r="B35" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>14</v>
@@ -6092,19 +6412,19 @@
         <v>3853</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>156</v>
+        <v>189</v>
       </c>
       <c r="L35" s="13">
-        <v>46125</v>
+        <v>46162</v>
       </c>
       <c r="M35" s="1">
         <v>1</v>
       </c>
       <c r="N35" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O35" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
@@ -6112,7 +6432,7 @@
         <v>2026</v>
       </c>
       <c r="B36" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>14</v>
@@ -6139,19 +6459,19 @@
         <v>3853</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="L36" s="13">
-        <v>46091</v>
+        <v>46049</v>
       </c>
       <c r="M36" s="1">
         <v>1</v>
       </c>
       <c r="N36" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O36" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.3">
@@ -6159,7 +6479,7 @@
         <v>2026</v>
       </c>
       <c r="B37" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>14</v>
@@ -6186,19 +6506,19 @@
         <v>3853</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>157</v>
+        <v>52</v>
       </c>
       <c r="L37" s="13">
-        <v>46121</v>
+        <v>46076</v>
       </c>
       <c r="M37" s="1">
         <v>1</v>
       </c>
       <c r="N37" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O37" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
@@ -6206,7 +6526,7 @@
         <v>2026</v>
       </c>
       <c r="B38" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>14</v>
@@ -6233,10 +6553,10 @@
         <v>3853</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>57</v>
+        <v>175</v>
       </c>
       <c r="L38" s="13">
-        <v>46047</v>
+        <v>46141</v>
       </c>
       <c r="M38" s="1">
         <v>1</v>
@@ -6253,7 +6573,7 @@
         <v>2026</v>
       </c>
       <c r="B39" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>14</v>
@@ -6280,19 +6600,19 @@
         <v>3853</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="L39" s="13">
-        <v>46084</v>
+        <v>46030</v>
       </c>
       <c r="M39" s="1">
         <v>1</v>
       </c>
       <c r="N39" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O39" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.3">
@@ -6300,7 +6620,7 @@
         <v>2026</v>
       </c>
       <c r="B40" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>14</v>
@@ -6327,19 +6647,19 @@
         <v>3853</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="L40" s="13">
-        <v>46036</v>
+        <v>46091</v>
       </c>
       <c r="M40" s="1">
         <v>1</v>
       </c>
       <c r="N40" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O40" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.3">
@@ -6347,46 +6667,46 @@
         <v>2026</v>
       </c>
       <c r="B41" s="1">
+        <v>4</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J41" s="1">
+        <v>3853</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="L41" s="13">
+        <v>46121</v>
+      </c>
+      <c r="M41" s="1">
+        <v>1</v>
+      </c>
+      <c r="N41" s="1">
+        <v>1</v>
+      </c>
+      <c r="O41" s="1">
         <v>3</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H41" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I41" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="J41" s="1">
-        <v>3853</v>
-      </c>
-      <c r="K41" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="L41" s="13">
-        <v>46097</v>
-      </c>
-      <c r="M41" s="1">
-        <v>1</v>
-      </c>
-      <c r="N41" s="1">
-        <v>0</v>
-      </c>
-      <c r="O41" s="1">
-        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.3">
@@ -6394,7 +6714,7 @@
         <v>2026</v>
       </c>
       <c r="B42" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>14</v>
@@ -6421,19 +6741,19 @@
         <v>3853</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="L42" s="13">
-        <v>46076</v>
+        <v>46047</v>
       </c>
       <c r="M42" s="1">
         <v>1</v>
       </c>
       <c r="N42" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O42" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.3">
@@ -6441,7 +6761,7 @@
         <v>2026</v>
       </c>
       <c r="B43" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>14</v>
@@ -6468,10 +6788,10 @@
         <v>3853</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="L43" s="13">
-        <v>46141</v>
+        <v>46159</v>
       </c>
       <c r="M43" s="1">
         <v>1</v>
@@ -6488,7 +6808,7 @@
         <v>2026</v>
       </c>
       <c r="B44" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>14</v>
@@ -6515,19 +6835,19 @@
         <v>3853</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="L44" s="13">
-        <v>46030</v>
+        <v>46084</v>
       </c>
       <c r="M44" s="1">
         <v>1</v>
       </c>
       <c r="N44" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O44" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.3">
@@ -6535,7 +6855,7 @@
         <v>2026</v>
       </c>
       <c r="B45" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>14</v>
@@ -6562,19 +6882,19 @@
         <v>3853</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="L45" s="13">
-        <v>46098</v>
+        <v>46036</v>
       </c>
       <c r="M45" s="1">
         <v>1</v>
       </c>
       <c r="N45" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O45" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.3">
@@ -6582,7 +6902,7 @@
         <v>2026</v>
       </c>
       <c r="B46" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>14</v>
@@ -6609,19 +6929,19 @@
         <v>3853</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="L46" s="13">
-        <v>46071</v>
+        <v>46097</v>
       </c>
       <c r="M46" s="1">
         <v>1</v>
       </c>
       <c r="N46" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O46" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.3">
@@ -6656,7 +6976,7 @@
         <v>3853</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="L47" s="13">
         <v>46076</v>
@@ -6676,7 +6996,7 @@
         <v>2026</v>
       </c>
       <c r="B48" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>14</v>
@@ -6703,19 +7023,19 @@
         <v>3853</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>68</v>
+        <v>191</v>
       </c>
       <c r="L48" s="13">
-        <v>46110</v>
+        <v>46166</v>
       </c>
       <c r="M48" s="1">
         <v>1</v>
       </c>
       <c r="N48" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O48" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.3">
@@ -6723,7 +7043,7 @@
         <v>2026</v>
       </c>
       <c r="B49" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>14</v>
@@ -6750,19 +7070,19 @@
         <v>3853</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="L49" s="13">
-        <v>46048</v>
+        <v>46098</v>
       </c>
       <c r="M49" s="1">
         <v>1</v>
       </c>
       <c r="N49" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O49" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.3">
@@ -6770,7 +7090,7 @@
         <v>2026</v>
       </c>
       <c r="B50" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>14</v>
@@ -6797,19 +7117,19 @@
         <v>3853</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="L50" s="13">
-        <v>46099</v>
+        <v>46071</v>
       </c>
       <c r="M50" s="1">
         <v>1</v>
       </c>
       <c r="N50" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O50" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.3">
@@ -6817,7 +7137,7 @@
         <v>2026</v>
       </c>
       <c r="B51" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>14</v>
@@ -6844,10 +7164,10 @@
         <v>3853</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>158</v>
+        <v>67</v>
       </c>
       <c r="L51" s="13">
-        <v>46135</v>
+        <v>46076</v>
       </c>
       <c r="M51" s="1">
         <v>1</v>
@@ -6856,7 +7176,7 @@
         <v>1</v>
       </c>
       <c r="O51" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.3">
@@ -6864,7 +7184,7 @@
         <v>2026</v>
       </c>
       <c r="B52" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>14</v>
@@ -6891,10 +7211,10 @@
         <v>3853</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>159</v>
+        <v>68</v>
       </c>
       <c r="L52" s="13">
-        <v>46134</v>
+        <v>46110</v>
       </c>
       <c r="M52" s="1">
         <v>1</v>
@@ -6903,7 +7223,7 @@
         <v>1</v>
       </c>
       <c r="O52" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.3">
@@ -6938,10 +7258,10 @@
         <v>3853</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="L53" s="13">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="M53" s="1">
         <v>1</v>
@@ -6950,7 +7270,7 @@
         <v>1</v>
       </c>
       <c r="O53" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.3">
@@ -6958,7 +7278,7 @@
         <v>2026</v>
       </c>
       <c r="B54" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>14</v>
@@ -6985,19 +7305,19 @@
         <v>3853</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>176</v>
+        <v>59</v>
       </c>
       <c r="L54" s="13">
-        <v>46140</v>
+        <v>46099</v>
       </c>
       <c r="M54" s="1">
         <v>1</v>
       </c>
       <c r="N54" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O54" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.3">
@@ -7005,7 +7325,7 @@
         <v>2026</v>
       </c>
       <c r="B55" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>14</v>
@@ -7032,19 +7352,19 @@
         <v>3853</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L55" s="13">
-        <v>46090</v>
+        <v>46047</v>
       </c>
       <c r="M55" s="1">
         <v>1</v>
       </c>
       <c r="N55" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O55" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.3">
@@ -7052,7 +7372,7 @@
         <v>2026</v>
       </c>
       <c r="B56" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>14</v>
@@ -7079,19 +7399,19 @@
         <v>3853</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>64</v>
+        <v>176</v>
       </c>
       <c r="L56" s="13">
-        <v>46095</v>
+        <v>46140</v>
       </c>
       <c r="M56" s="1">
         <v>1</v>
       </c>
       <c r="N56" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O56" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.3">
@@ -7099,7 +7419,7 @@
         <v>2026</v>
       </c>
       <c r="B57" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>14</v>
@@ -7126,19 +7446,19 @@
         <v>3853</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="L57" s="13">
-        <v>46035</v>
+        <v>46090</v>
       </c>
       <c r="M57" s="1">
         <v>1</v>
       </c>
       <c r="N57" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O57" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.3">
@@ -7146,7 +7466,7 @@
         <v>2026</v>
       </c>
       <c r="B58" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>14</v>
@@ -7173,19 +7493,19 @@
         <v>3853</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>69</v>
+        <v>192</v>
       </c>
       <c r="L58" s="13">
-        <v>46045</v>
+        <v>46155</v>
       </c>
       <c r="M58" s="1">
         <v>1</v>
       </c>
       <c r="N58" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O58" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.3">
@@ -7193,7 +7513,7 @@
         <v>2026</v>
       </c>
       <c r="B59" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>14</v>
@@ -7220,19 +7540,19 @@
         <v>3853</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="L59" s="13">
-        <v>46032</v>
+        <v>46095</v>
       </c>
       <c r="M59" s="1">
         <v>1</v>
       </c>
       <c r="N59" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O59" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.3">
@@ -7240,7 +7560,7 @@
         <v>2026</v>
       </c>
       <c r="B60" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>14</v>
@@ -7267,10 +7587,10 @@
         <v>3853</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>71</v>
+        <v>193</v>
       </c>
       <c r="L60" s="13">
-        <v>46042</v>
+        <v>46164</v>
       </c>
       <c r="M60" s="1">
         <v>1</v>
@@ -7287,46 +7607,46 @@
         <v>2026</v>
       </c>
       <c r="B61" s="1">
+        <v>1</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J61" s="1">
+        <v>3853</v>
+      </c>
+      <c r="K61" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="L61" s="13">
+        <v>46032</v>
+      </c>
+      <c r="M61" s="1">
+        <v>1</v>
+      </c>
+      <c r="N61" s="1">
+        <v>1</v>
+      </c>
+      <c r="O61" s="1">
         <v>2</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G61" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H61" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I61" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="J61" s="1">
-        <v>3853</v>
-      </c>
-      <c r="K61" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="L61" s="13">
-        <v>46061</v>
-      </c>
-      <c r="M61" s="1">
-        <v>1</v>
-      </c>
-      <c r="N61" s="1">
-        <v>1</v>
-      </c>
-      <c r="O61" s="1">
-        <v>3</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.3">
@@ -7334,7 +7654,7 @@
         <v>2026</v>
       </c>
       <c r="B62" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>14</v>
@@ -7361,10 +7681,10 @@
         <v>3853</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>179</v>
+        <v>71</v>
       </c>
       <c r="L62" s="13">
-        <v>46148</v>
+        <v>46042</v>
       </c>
       <c r="M62" s="1">
         <v>1</v>
@@ -7381,46 +7701,46 @@
         <v>2026</v>
       </c>
       <c r="B63" s="1">
+        <v>2</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J63" s="1">
+        <v>3853</v>
+      </c>
+      <c r="K63" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L63" s="13">
+        <v>46061</v>
+      </c>
+      <c r="M63" s="1">
+        <v>1</v>
+      </c>
+      <c r="N63" s="1">
+        <v>1</v>
+      </c>
+      <c r="O63" s="1">
         <v>4</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F63" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G63" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H63" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I63" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="J63" s="1">
-        <v>3853</v>
-      </c>
-      <c r="K63" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="L63" s="13">
-        <v>46120</v>
-      </c>
-      <c r="M63" s="1">
-        <v>1</v>
-      </c>
-      <c r="N63" s="1">
-        <v>0</v>
-      </c>
-      <c r="O63" s="1">
-        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.3">
@@ -7455,7 +7775,7 @@
         <v>3853</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="L64" s="13">
         <v>46148</v>
@@ -7467,7 +7787,7 @@
         <v>1</v>
       </c>
       <c r="O64" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.3">
@@ -7502,19 +7822,19 @@
         <v>3853</v>
       </c>
       <c r="K65" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="L65" s="13">
-        <v>46136</v>
+        <v>46135</v>
       </c>
       <c r="M65" s="1">
         <v>1</v>
       </c>
       <c r="N65" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O65" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.3">
@@ -7522,7 +7842,7 @@
         <v>2026</v>
       </c>
       <c r="B66" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>14</v>
@@ -7549,10 +7869,10 @@
         <v>3853</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>77</v>
+        <v>159</v>
       </c>
       <c r="L66" s="13">
-        <v>46050</v>
+        <v>46134</v>
       </c>
       <c r="M66" s="1">
         <v>1</v>
@@ -7561,7 +7881,7 @@
         <v>1</v>
       </c>
       <c r="O66" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.3">
@@ -7569,7 +7889,7 @@
         <v>2026</v>
       </c>
       <c r="B67" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>14</v>
@@ -7596,19 +7916,19 @@
         <v>3853</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>78</v>
+        <v>160</v>
       </c>
       <c r="L67" s="13">
-        <v>46070</v>
+        <v>46136</v>
       </c>
       <c r="M67" s="1">
         <v>1</v>
       </c>
       <c r="N67" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O67" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.3">
@@ -7616,7 +7936,7 @@
         <v>2026</v>
       </c>
       <c r="B68" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>14</v>
@@ -7643,19 +7963,19 @@
         <v>3853</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L68" s="13">
-        <v>46067</v>
+        <v>46050</v>
       </c>
       <c r="M68" s="1">
         <v>1</v>
       </c>
       <c r="N68" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O68" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.3">
@@ -7690,10 +8010,10 @@
         <v>3853</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="L69" s="13">
-        <v>46060</v>
+        <v>46070</v>
       </c>
       <c r="M69" s="1">
         <v>1</v>
@@ -7702,7 +8022,7 @@
         <v>1</v>
       </c>
       <c r="O69" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.3">
@@ -7737,10 +8057,10 @@
         <v>3853</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="L70" s="13">
-        <v>46074</v>
+        <v>46067</v>
       </c>
       <c r="M70" s="1">
         <v>1</v>
@@ -7757,46 +8077,46 @@
         <v>2026</v>
       </c>
       <c r="B71" s="1">
+        <v>1</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J71" s="1">
+        <v>3853</v>
+      </c>
+      <c r="K71" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="L71" s="13">
+        <v>46035</v>
+      </c>
+      <c r="M71" s="1">
+        <v>1</v>
+      </c>
+      <c r="N71" s="1">
+        <v>1</v>
+      </c>
+      <c r="O71" s="1">
         <v>2</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F71" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G71" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H71" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I71" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="J71" s="1">
-        <v>3853</v>
-      </c>
-      <c r="K71" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="L71" s="13">
-        <v>46070</v>
-      </c>
-      <c r="M71" s="1">
-        <v>1</v>
-      </c>
-      <c r="N71" s="1">
-        <v>0</v>
-      </c>
-      <c r="O71" s="1">
-        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.3">
@@ -7804,7 +8124,7 @@
         <v>2026</v>
       </c>
       <c r="B72" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>14</v>
@@ -7831,10 +8151,10 @@
         <v>3853</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>161</v>
+        <v>69</v>
       </c>
       <c r="L72" s="13">
-        <v>46132</v>
+        <v>46045</v>
       </c>
       <c r="M72" s="1">
         <v>1</v>
@@ -7843,7 +8163,7 @@
         <v>1</v>
       </c>
       <c r="O72" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.3">
@@ -7851,7 +8171,7 @@
         <v>2026</v>
       </c>
       <c r="B73" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>14</v>
@@ -7878,19 +8198,19 @@
         <v>3853</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>162</v>
+        <v>75</v>
       </c>
       <c r="L73" s="13">
-        <v>46129</v>
+        <v>46070</v>
       </c>
       <c r="M73" s="1">
         <v>1</v>
       </c>
       <c r="N73" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O73" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.3">
@@ -7898,7 +8218,7 @@
         <v>2026</v>
       </c>
       <c r="B74" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>14</v>
@@ -7925,19 +8245,19 @@
         <v>3853</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>76</v>
+        <v>161</v>
       </c>
       <c r="L74" s="13">
-        <v>46070</v>
+        <v>46132</v>
       </c>
       <c r="M74" s="1">
         <v>1</v>
       </c>
       <c r="N74" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O74" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.3">
@@ -7945,46 +8265,46 @@
         <v>2026</v>
       </c>
       <c r="B75" s="1">
+        <v>4</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I75" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J75" s="1">
+        <v>3853</v>
+      </c>
+      <c r="K75" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="L75" s="13">
+        <v>46129</v>
+      </c>
+      <c r="M75" s="1">
+        <v>1</v>
+      </c>
+      <c r="N75" s="1">
+        <v>1</v>
+      </c>
+      <c r="O75" s="1">
         <v>3</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F75" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G75" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H75" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I75" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="J75" s="1">
-        <v>3853</v>
-      </c>
-      <c r="K75" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="L75" s="13">
-        <v>46100</v>
-      </c>
-      <c r="M75" s="1">
-        <v>1</v>
-      </c>
-      <c r="N75" s="1">
-        <v>0</v>
-      </c>
-      <c r="O75" s="1">
-        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.3">
@@ -7992,7 +8312,7 @@
         <v>2026</v>
       </c>
       <c r="B76" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>14</v>
@@ -8019,19 +8339,19 @@
         <v>3853</v>
       </c>
       <c r="K76" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="L76" s="13">
-        <v>46086</v>
+        <v>46070</v>
       </c>
       <c r="M76" s="1">
         <v>1</v>
       </c>
       <c r="N76" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O76" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.3">
@@ -8039,7 +8359,7 @@
         <v>2026</v>
       </c>
       <c r="B77" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>14</v>
@@ -8066,19 +8386,19 @@
         <v>3853</v>
       </c>
       <c r="K77" s="1" t="s">
-        <v>82</v>
+        <v>150</v>
       </c>
       <c r="L77" s="13">
-        <v>46063</v>
+        <v>46120</v>
       </c>
       <c r="M77" s="1">
         <v>1</v>
       </c>
       <c r="N77" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O77" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.3">
@@ -8086,7 +8406,7 @@
         <v>2026</v>
       </c>
       <c r="B78" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>14</v>
@@ -8113,19 +8433,19 @@
         <v>3853</v>
       </c>
       <c r="K78" s="1" t="s">
-        <v>83</v>
+        <v>180</v>
       </c>
       <c r="L78" s="13">
-        <v>46029</v>
+        <v>46148</v>
       </c>
       <c r="M78" s="1">
         <v>1</v>
       </c>
       <c r="N78" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O78" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.3">
@@ -8133,7 +8453,7 @@
         <v>2026</v>
       </c>
       <c r="B79" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>14</v>
@@ -8160,10 +8480,10 @@
         <v>3853</v>
       </c>
       <c r="K79" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L79" s="13">
-        <v>46049</v>
+        <v>46063</v>
       </c>
       <c r="M79" s="1">
         <v>1</v>
@@ -8172,7 +8492,7 @@
         <v>1</v>
       </c>
       <c r="O79" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.3">
@@ -8180,7 +8500,7 @@
         <v>2026</v>
       </c>
       <c r="B80" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>14</v>
@@ -8207,19 +8527,19 @@
         <v>3853</v>
       </c>
       <c r="K80" s="1" t="s">
-        <v>163</v>
+        <v>83</v>
       </c>
       <c r="L80" s="13">
-        <v>46129</v>
+        <v>46029</v>
       </c>
       <c r="M80" s="1">
         <v>1</v>
       </c>
       <c r="N80" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O80" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.3">
@@ -8227,7 +8547,7 @@
         <v>2026</v>
       </c>
       <c r="B81" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>14</v>
@@ -8254,10 +8574,10 @@
         <v>3853</v>
       </c>
       <c r="K81" s="1" t="s">
-        <v>165</v>
+        <v>84</v>
       </c>
       <c r="L81" s="13">
-        <v>46134</v>
+        <v>46049</v>
       </c>
       <c r="M81" s="1">
         <v>1</v>
@@ -8266,7 +8586,7 @@
         <v>1</v>
       </c>
       <c r="O81" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.3">
@@ -8274,7 +8594,7 @@
         <v>2026</v>
       </c>
       <c r="B82" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>14</v>
@@ -8301,19 +8621,19 @@
         <v>3853</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>90</v>
+        <v>163</v>
       </c>
       <c r="L82" s="13">
-        <v>46080</v>
+        <v>46129</v>
       </c>
       <c r="M82" s="1">
         <v>1</v>
       </c>
       <c r="N82" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O82" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.3">
@@ -8321,7 +8641,7 @@
         <v>2026</v>
       </c>
       <c r="B83" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>14</v>
@@ -8348,19 +8668,19 @@
         <v>3853</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>181</v>
+        <v>85</v>
       </c>
       <c r="L83" s="13">
-        <v>46147</v>
+        <v>46060</v>
       </c>
       <c r="M83" s="1">
         <v>1</v>
       </c>
       <c r="N83" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O83" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.3">
@@ -8368,7 +8688,7 @@
         <v>2026</v>
       </c>
       <c r="B84" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>14</v>
@@ -8395,19 +8715,19 @@
         <v>3853</v>
       </c>
       <c r="K84" s="1" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="L84" s="13">
-        <v>46048</v>
+        <v>46074</v>
       </c>
       <c r="M84" s="1">
         <v>1</v>
       </c>
       <c r="N84" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O84" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.3">
@@ -8415,7 +8735,7 @@
         <v>2026</v>
       </c>
       <c r="B85" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>14</v>
@@ -8442,10 +8762,10 @@
         <v>3853</v>
       </c>
       <c r="K85" s="1" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="L85" s="13">
-        <v>46141</v>
+        <v>46147</v>
       </c>
       <c r="M85" s="1">
         <v>1</v>
@@ -8462,7 +8782,7 @@
         <v>2026</v>
       </c>
       <c r="B86" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>14</v>
@@ -8489,19 +8809,19 @@
         <v>3853</v>
       </c>
       <c r="K86" s="1" t="s">
-        <v>166</v>
+        <v>91</v>
       </c>
       <c r="L86" s="13">
-        <v>46121</v>
+        <v>46048</v>
       </c>
       <c r="M86" s="1">
         <v>1</v>
       </c>
       <c r="N86" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O86" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.3">
@@ -8509,7 +8829,7 @@
         <v>2026</v>
       </c>
       <c r="B87" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>14</v>
@@ -8536,10 +8856,10 @@
         <v>3853</v>
       </c>
       <c r="K87" s="1" t="s">
-        <v>96</v>
+        <v>177</v>
       </c>
       <c r="L87" s="13">
-        <v>46050</v>
+        <v>46141</v>
       </c>
       <c r="M87" s="1">
         <v>1</v>
@@ -8556,7 +8876,7 @@
         <v>2026</v>
       </c>
       <c r="B88" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>14</v>
@@ -8583,19 +8903,19 @@
         <v>3853</v>
       </c>
       <c r="K88" s="1" t="s">
-        <v>97</v>
+        <v>166</v>
       </c>
       <c r="L88" s="13">
-        <v>46049</v>
+        <v>46121</v>
       </c>
       <c r="M88" s="1">
         <v>1</v>
       </c>
       <c r="N88" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O88" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.3">
@@ -8603,7 +8923,7 @@
         <v>2026</v>
       </c>
       <c r="B89" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>14</v>
@@ -8630,19 +8950,19 @@
         <v>3853</v>
       </c>
       <c r="K89" s="1" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="L89" s="13">
-        <v>46047</v>
+        <v>46100</v>
       </c>
       <c r="M89" s="1">
         <v>1</v>
       </c>
       <c r="N89" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O89" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.3">
@@ -8650,7 +8970,7 @@
         <v>2026</v>
       </c>
       <c r="B90" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>14</v>
@@ -8677,10 +8997,10 @@
         <v>3853</v>
       </c>
       <c r="K90" s="1" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="L90" s="13">
-        <v>46078</v>
+        <v>46086</v>
       </c>
       <c r="M90" s="1">
         <v>1</v>
@@ -8689,7 +9009,7 @@
         <v>1</v>
       </c>
       <c r="O90" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.3">
@@ -8744,7 +9064,7 @@
         <v>2026</v>
       </c>
       <c r="B92" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>14</v>
@@ -8771,10 +9091,10 @@
         <v>3853</v>
       </c>
       <c r="K92" s="1" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="L92" s="13">
-        <v>46138</v>
+        <v>46164</v>
       </c>
       <c r="M92" s="1">
         <v>1</v>
@@ -8818,10 +9138,10 @@
         <v>3853</v>
       </c>
       <c r="K93" s="1" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="L93" s="13">
-        <v>46119</v>
+        <v>46138</v>
       </c>
       <c r="M93" s="1">
         <v>1</v>
@@ -8838,7 +9158,7 @@
         <v>2026</v>
       </c>
       <c r="B94" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>14</v>
@@ -8865,19 +9185,19 @@
         <v>3853</v>
       </c>
       <c r="K94" s="1" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="L94" s="13">
-        <v>46149</v>
+        <v>46134</v>
       </c>
       <c r="M94" s="1">
         <v>1</v>
       </c>
       <c r="N94" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O94" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.3">
@@ -8885,7 +9205,7 @@
         <v>2026</v>
       </c>
       <c r="B95" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>14</v>
@@ -8912,19 +9232,19 @@
         <v>3853</v>
       </c>
       <c r="K95" s="1" t="s">
-        <v>93</v>
+        <v>195</v>
       </c>
       <c r="L95" s="13">
-        <v>46043</v>
+        <v>46155</v>
       </c>
       <c r="M95" s="1">
         <v>1</v>
       </c>
       <c r="N95" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O95" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.3">
@@ -8932,7 +9252,7 @@
         <v>2026</v>
       </c>
       <c r="B96" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>14</v>
@@ -8959,19 +9279,19 @@
         <v>3853</v>
       </c>
       <c r="K96" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="L96" s="13">
-        <v>46110</v>
+        <v>46080</v>
       </c>
       <c r="M96" s="1">
         <v>1</v>
       </c>
       <c r="N96" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O96" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.3">
@@ -8979,7 +9299,7 @@
         <v>2026</v>
       </c>
       <c r="B97" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>14</v>
@@ -9006,19 +9326,19 @@
         <v>3853</v>
       </c>
       <c r="K97" s="1" t="s">
-        <v>95</v>
+        <v>183</v>
       </c>
       <c r="L97" s="13">
-        <v>46043</v>
+        <v>46161</v>
       </c>
       <c r="M97" s="1">
         <v>1</v>
       </c>
       <c r="N97" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O97" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.3">
@@ -9026,7 +9346,7 @@
         <v>2026</v>
       </c>
       <c r="B98" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>14</v>
@@ -9053,19 +9373,19 @@
         <v>3853</v>
       </c>
       <c r="K98" s="1" t="s">
-        <v>183</v>
+        <v>96</v>
       </c>
       <c r="L98" s="13">
-        <v>46151</v>
+        <v>46050</v>
       </c>
       <c r="M98" s="1">
         <v>1</v>
       </c>
       <c r="N98" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O98" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.3">
@@ -9100,10 +9420,10 @@
         <v>3853</v>
       </c>
       <c r="K99" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="L99" s="13">
-        <v>46043</v>
+        <v>46049</v>
       </c>
       <c r="M99" s="1">
         <v>1</v>
@@ -9112,7 +9432,7 @@
         <v>1</v>
       </c>
       <c r="O99" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.3">
@@ -9120,7 +9440,7 @@
         <v>2026</v>
       </c>
       <c r="B100" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>14</v>
@@ -9147,19 +9467,19 @@
         <v>3853</v>
       </c>
       <c r="K100" s="1" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="L100" s="13">
-        <v>46077</v>
+        <v>46047</v>
       </c>
       <c r="M100" s="1">
         <v>1</v>
       </c>
       <c r="N100" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O100" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.3">
@@ -9194,10 +9514,10 @@
         <v>3853</v>
       </c>
       <c r="K101" s="1" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="L101" s="13">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="M101" s="1">
         <v>1</v>
@@ -9206,7 +9526,7 @@
         <v>1</v>
       </c>
       <c r="O101" s="1">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.3">
@@ -9214,7 +9534,7 @@
         <v>2026</v>
       </c>
       <c r="B102" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>14</v>
@@ -9241,19 +9561,19 @@
         <v>3853</v>
       </c>
       <c r="K102" s="1" t="s">
-        <v>167</v>
+        <v>196</v>
       </c>
       <c r="L102" s="13">
-        <v>46136</v>
+        <v>46156</v>
       </c>
       <c r="M102" s="1">
         <v>1</v>
       </c>
       <c r="N102" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O102" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.3">
@@ -9261,7 +9581,7 @@
         <v>2026</v>
       </c>
       <c r="B103" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>14</v>
@@ -9288,10 +9608,10 @@
         <v>3853</v>
       </c>
       <c r="K103" s="1" t="s">
-        <v>103</v>
+        <v>151</v>
       </c>
       <c r="L103" s="13">
-        <v>46067</v>
+        <v>46119</v>
       </c>
       <c r="M103" s="1">
         <v>1</v>
@@ -9308,7 +9628,7 @@
         <v>2026</v>
       </c>
       <c r="B104" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>14</v>
@@ -9335,19 +9655,19 @@
         <v>3853</v>
       </c>
       <c r="K104" s="1" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="L104" s="13">
-        <v>46137</v>
+        <v>46149</v>
       </c>
       <c r="M104" s="1">
         <v>1</v>
       </c>
       <c r="N104" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O104" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105" spans="1:15" x14ac:dyDescent="0.3">
@@ -9382,19 +9702,19 @@
         <v>3853</v>
       </c>
       <c r="K105" s="1" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="L105" s="13">
-        <v>46028</v>
+        <v>46043</v>
       </c>
       <c r="M105" s="1">
         <v>1</v>
       </c>
       <c r="N105" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O105" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.3">
@@ -9402,7 +9722,7 @@
         <v>2026</v>
       </c>
       <c r="B106" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>14</v>
@@ -9429,10 +9749,10 @@
         <v>3853</v>
       </c>
       <c r="K106" s="1" t="s">
-        <v>108</v>
+        <v>197</v>
       </c>
       <c r="L106" s="13">
-        <v>46107</v>
+        <v>46165</v>
       </c>
       <c r="M106" s="1">
         <v>1</v>
@@ -9449,7 +9769,7 @@
         <v>2026</v>
       </c>
       <c r="B107" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>14</v>
@@ -9476,10 +9796,10 @@
         <v>3853</v>
       </c>
       <c r="K107" s="1" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="L107" s="13">
-        <v>46034</v>
+        <v>46110</v>
       </c>
       <c r="M107" s="1">
         <v>1</v>
@@ -9488,7 +9808,7 @@
         <v>1</v>
       </c>
       <c r="O107" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108" spans="1:15" x14ac:dyDescent="0.3">
@@ -9496,7 +9816,7 @@
         <v>2026</v>
       </c>
       <c r="B108" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>14</v>
@@ -9523,10 +9843,10 @@
         <v>3853</v>
       </c>
       <c r="K108" s="1" t="s">
-        <v>178</v>
+        <v>95</v>
       </c>
       <c r="L108" s="13">
-        <v>46141</v>
+        <v>46043</v>
       </c>
       <c r="M108" s="1">
         <v>1</v>
@@ -9535,7 +9855,7 @@
         <v>1</v>
       </c>
       <c r="O108" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109" spans="1:15" x14ac:dyDescent="0.3">
@@ -9543,7 +9863,7 @@
         <v>2026</v>
       </c>
       <c r="B109" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>14</v>
@@ -9570,19 +9890,19 @@
         <v>3853</v>
       </c>
       <c r="K109" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L109" s="13">
-        <v>46097</v>
+        <v>46077</v>
       </c>
       <c r="M109" s="1">
         <v>1</v>
       </c>
       <c r="N109" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O109" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:15" x14ac:dyDescent="0.3">
@@ -9617,19 +9937,19 @@
         <v>3853</v>
       </c>
       <c r="K110" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="L110" s="13">
-        <v>46070</v>
+        <v>46077</v>
       </c>
       <c r="M110" s="1">
         <v>1</v>
       </c>
       <c r="N110" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O110" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111" spans="1:15" x14ac:dyDescent="0.3">
@@ -9637,7 +9957,7 @@
         <v>2026</v>
       </c>
       <c r="B111" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>14</v>
@@ -9664,19 +9984,19 @@
         <v>3853</v>
       </c>
       <c r="K111" s="1" t="s">
-        <v>115</v>
+        <v>167</v>
       </c>
       <c r="L111" s="13">
-        <v>46098</v>
+        <v>46136</v>
       </c>
       <c r="M111" s="1">
         <v>1</v>
       </c>
       <c r="N111" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O111" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="112" spans="1:15" x14ac:dyDescent="0.3">
@@ -9684,7 +10004,7 @@
         <v>2026</v>
       </c>
       <c r="B112" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>14</v>
@@ -9711,10 +10031,10 @@
         <v>3853</v>
       </c>
       <c r="K112" s="1" t="s">
-        <v>170</v>
+        <v>198</v>
       </c>
       <c r="L112" s="13">
-        <v>46121</v>
+        <v>46157</v>
       </c>
       <c r="M112" s="1">
         <v>1</v>
@@ -9731,7 +10051,7 @@
         <v>2026</v>
       </c>
       <c r="B113" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>14</v>
@@ -9758,19 +10078,19 @@
         <v>3853</v>
       </c>
       <c r="K113" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L113" s="13">
-        <v>46044</v>
+        <v>46067</v>
       </c>
       <c r="M113" s="1">
         <v>1</v>
       </c>
       <c r="N113" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O113" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:15" x14ac:dyDescent="0.3">
@@ -9778,7 +10098,7 @@
         <v>2026</v>
       </c>
       <c r="B114" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>14</v>
@@ -9805,10 +10125,10 @@
         <v>3853</v>
       </c>
       <c r="K114" s="1" t="s">
-        <v>105</v>
+        <v>168</v>
       </c>
       <c r="L114" s="13">
-        <v>46084</v>
+        <v>46137</v>
       </c>
       <c r="M114" s="1">
         <v>1</v>
@@ -9825,7 +10145,7 @@
         <v>2026</v>
       </c>
       <c r="B115" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>14</v>
@@ -9852,19 +10172,19 @@
         <v>3853</v>
       </c>
       <c r="K115" s="1" t="s">
-        <v>152</v>
+        <v>108</v>
       </c>
       <c r="L115" s="13">
-        <v>46115</v>
+        <v>46107</v>
       </c>
       <c r="M115" s="1">
         <v>1</v>
       </c>
       <c r="N115" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O115" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:15" x14ac:dyDescent="0.3">
@@ -9872,7 +10192,7 @@
         <v>2026</v>
       </c>
       <c r="B116" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>14</v>
@@ -9899,10 +10219,10 @@
         <v>3853</v>
       </c>
       <c r="K116" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="L116" s="13">
-        <v>46089</v>
+        <v>46034</v>
       </c>
       <c r="M116" s="1">
         <v>1</v>
@@ -9911,7 +10231,7 @@
         <v>1</v>
       </c>
       <c r="O116" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="117" spans="1:15" x14ac:dyDescent="0.3">
@@ -9919,46 +10239,46 @@
         <v>2026</v>
       </c>
       <c r="B117" s="1">
+        <v>4</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G117" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H117" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I117" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J117" s="1">
+        <v>3853</v>
+      </c>
+      <c r="K117" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="L117" s="13">
+        <v>46141</v>
+      </c>
+      <c r="M117" s="1">
+        <v>1</v>
+      </c>
+      <c r="N117" s="1">
+        <v>1</v>
+      </c>
+      <c r="O117" s="1">
         <v>2</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E117" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F117" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G117" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H117" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I117" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="J117" s="1">
-        <v>3853</v>
-      </c>
-      <c r="K117" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="L117" s="13">
-        <v>46065</v>
-      </c>
-      <c r="M117" s="1">
-        <v>1</v>
-      </c>
-      <c r="N117" s="1">
-        <v>1</v>
-      </c>
-      <c r="O117" s="1">
-        <v>5</v>
       </c>
     </row>
     <row r="118" spans="1:15" x14ac:dyDescent="0.3">
@@ -9993,10 +10313,10 @@
         <v>3853</v>
       </c>
       <c r="K118" s="1" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="L118" s="13">
-        <v>46084</v>
+        <v>46097</v>
       </c>
       <c r="M118" s="1">
         <v>1</v>
@@ -10005,7 +10325,7 @@
         <v>1</v>
       </c>
       <c r="O118" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="119" spans="1:15" x14ac:dyDescent="0.3">
@@ -10013,7 +10333,7 @@
         <v>2026</v>
       </c>
       <c r="B119" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>14</v>
@@ -10040,10 +10360,10 @@
         <v>3853</v>
       </c>
       <c r="K119" s="1" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="L119" s="13">
-        <v>46085</v>
+        <v>46070</v>
       </c>
       <c r="M119" s="1">
         <v>1</v>
@@ -10060,7 +10380,7 @@
         <v>2026</v>
       </c>
       <c r="B120" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>14</v>
@@ -10087,19 +10407,19 @@
         <v>3853</v>
       </c>
       <c r="K120" s="1" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="L120" s="13">
-        <v>46060</v>
+        <v>46043</v>
       </c>
       <c r="M120" s="1">
         <v>1</v>
       </c>
       <c r="N120" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O120" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="121" spans="1:15" x14ac:dyDescent="0.3">
@@ -10107,7 +10427,7 @@
         <v>2026</v>
       </c>
       <c r="B121" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>14</v>
@@ -10134,19 +10454,19 @@
         <v>3853</v>
       </c>
       <c r="K121" s="1" t="s">
-        <v>114</v>
+        <v>199</v>
       </c>
       <c r="L121" s="13">
-        <v>46092</v>
+        <v>46162</v>
       </c>
       <c r="M121" s="1">
         <v>1</v>
       </c>
       <c r="N121" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O121" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:15" x14ac:dyDescent="0.3">
@@ -10154,7 +10474,7 @@
         <v>2026</v>
       </c>
       <c r="B122" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>14</v>
@@ -10181,19 +10501,19 @@
         <v>3853</v>
       </c>
       <c r="K122" s="1" t="s">
-        <v>169</v>
+        <v>104</v>
       </c>
       <c r="L122" s="13">
-        <v>46135</v>
+        <v>46044</v>
       </c>
       <c r="M122" s="1">
         <v>1</v>
       </c>
       <c r="N122" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O122" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="123" spans="1:15" x14ac:dyDescent="0.3">
@@ -10201,7 +10521,7 @@
         <v>2026</v>
       </c>
       <c r="B123" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>14</v>
@@ -10228,19 +10548,19 @@
         <v>3853</v>
       </c>
       <c r="K123" s="1" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="L123" s="13">
-        <v>46024</v>
+        <v>46084</v>
       </c>
       <c r="M123" s="1">
         <v>1</v>
       </c>
       <c r="N123" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O123" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:15" x14ac:dyDescent="0.3">
@@ -10248,7 +10568,7 @@
         <v>2026</v>
       </c>
       <c r="B124" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>14</v>
@@ -10275,10 +10595,10 @@
         <v>3853</v>
       </c>
       <c r="K124" s="1" t="s">
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="L124" s="13">
-        <v>46035</v>
+        <v>46115</v>
       </c>
       <c r="M124" s="1">
         <v>1</v>
@@ -10287,7 +10607,7 @@
         <v>1</v>
       </c>
       <c r="O124" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="125" spans="1:15" x14ac:dyDescent="0.3">
@@ -10322,10 +10642,10 @@
         <v>3853</v>
       </c>
       <c r="K125" s="1" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="L125" s="13">
-        <v>46086</v>
+        <v>46089</v>
       </c>
       <c r="M125" s="1">
         <v>1</v>
@@ -10334,7 +10654,7 @@
         <v>1</v>
       </c>
       <c r="O125" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="126" spans="1:15" x14ac:dyDescent="0.3">
@@ -10369,10 +10689,10 @@
         <v>3853</v>
       </c>
       <c r="K126" s="1" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="L126" s="13">
-        <v>46032</v>
+        <v>46028</v>
       </c>
       <c r="M126" s="1">
         <v>1</v>
@@ -10389,7 +10709,7 @@
         <v>2026</v>
       </c>
       <c r="B127" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>14</v>
@@ -10416,19 +10736,19 @@
         <v>3853</v>
       </c>
       <c r="K127" s="1" t="s">
-        <v>171</v>
+        <v>112</v>
       </c>
       <c r="L127" s="13">
-        <v>46123</v>
+        <v>46085</v>
       </c>
       <c r="M127" s="1">
         <v>1</v>
       </c>
       <c r="N127" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O127" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:15" x14ac:dyDescent="0.3">
@@ -10436,7 +10756,7 @@
         <v>2026</v>
       </c>
       <c r="B128" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>14</v>
@@ -10463,19 +10783,19 @@
         <v>3853</v>
       </c>
       <c r="K128" s="1" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="L128" s="13">
-        <v>46031</v>
+        <v>46060</v>
       </c>
       <c r="M128" s="1">
         <v>1</v>
       </c>
       <c r="N128" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O128" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:15" x14ac:dyDescent="0.3">
@@ -10483,7 +10803,7 @@
         <v>2026</v>
       </c>
       <c r="B129" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>14</v>
@@ -10510,10 +10830,10 @@
         <v>3853</v>
       </c>
       <c r="K129" s="1" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="L129" s="13">
-        <v>46050</v>
+        <v>46092</v>
       </c>
       <c r="M129" s="1">
         <v>1</v>
@@ -10522,7 +10842,7 @@
         <v>1</v>
       </c>
       <c r="O129" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130" spans="1:15" x14ac:dyDescent="0.3">
@@ -10530,7 +10850,7 @@
         <v>2026</v>
       </c>
       <c r="B130" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>14</v>
@@ -10557,19 +10877,19 @@
         <v>3853</v>
       </c>
       <c r="K130" s="1" t="s">
-        <v>124</v>
+        <v>169</v>
       </c>
       <c r="L130" s="13">
-        <v>46030</v>
+        <v>46135</v>
       </c>
       <c r="M130" s="1">
         <v>1</v>
       </c>
       <c r="N130" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O130" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:15" x14ac:dyDescent="0.3">
@@ -10604,19 +10924,19 @@
         <v>3853</v>
       </c>
       <c r="K131" s="1" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="L131" s="13">
-        <v>46096</v>
+        <v>46098</v>
       </c>
       <c r="M131" s="1">
         <v>1</v>
       </c>
       <c r="N131" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O131" s="1">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:15" x14ac:dyDescent="0.3">
@@ -10624,7 +10944,7 @@
         <v>2026</v>
       </c>
       <c r="B132" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>14</v>
@@ -10651,19 +10971,19 @@
         <v>3853</v>
       </c>
       <c r="K132" s="1" t="s">
-        <v>126</v>
+        <v>170</v>
       </c>
       <c r="L132" s="13">
-        <v>46062</v>
+        <v>46121</v>
       </c>
       <c r="M132" s="1">
         <v>1</v>
       </c>
       <c r="N132" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O132" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133" spans="1:15" x14ac:dyDescent="0.3">
@@ -10698,10 +11018,10 @@
         <v>3853</v>
       </c>
       <c r="K133" s="1" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="L133" s="13">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="M133" s="1">
         <v>1</v>
@@ -10710,7 +11030,7 @@
         <v>1</v>
       </c>
       <c r="O133" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134" spans="1:15" x14ac:dyDescent="0.3">
@@ -10718,46 +11038,46 @@
         <v>2026</v>
       </c>
       <c r="B134" s="1">
+        <v>1</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G134" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H134" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I134" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J134" s="1">
+        <v>3853</v>
+      </c>
+      <c r="K134" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="L134" s="13">
+        <v>46032</v>
+      </c>
+      <c r="M134" s="1">
+        <v>1</v>
+      </c>
+      <c r="N134" s="1">
+        <v>1</v>
+      </c>
+      <c r="O134" s="1">
         <v>3</v>
-      </c>
-      <c r="C134" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D134" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E134" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F134" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G134" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H134" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I134" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="J134" s="1">
-        <v>3853</v>
-      </c>
-      <c r="K134" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="L134" s="13">
-        <v>46107</v>
-      </c>
-      <c r="M134" s="1">
-        <v>1</v>
-      </c>
-      <c r="N134" s="1">
-        <v>0</v>
-      </c>
-      <c r="O134" s="1">
-        <v>0</v>
       </c>
     </row>
     <row r="135" spans="1:15" x14ac:dyDescent="0.3">
@@ -10765,7 +11085,7 @@
         <v>2026</v>
       </c>
       <c r="B135" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>14</v>
@@ -10792,10 +11112,10 @@
         <v>3853</v>
       </c>
       <c r="K135" s="1" t="s">
-        <v>130</v>
+        <v>171</v>
       </c>
       <c r="L135" s="13">
-        <v>46034</v>
+        <v>46123</v>
       </c>
       <c r="M135" s="1">
         <v>1</v>
@@ -10804,7 +11124,7 @@
         <v>1</v>
       </c>
       <c r="O135" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="136" spans="1:15" x14ac:dyDescent="0.3">
@@ -10812,7 +11132,7 @@
         <v>2026</v>
       </c>
       <c r="B136" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>14</v>
@@ -10839,19 +11159,19 @@
         <v>3853</v>
       </c>
       <c r="K136" s="1" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="L136" s="13">
-        <v>46062</v>
+        <v>46031</v>
       </c>
       <c r="M136" s="1">
         <v>1</v>
       </c>
       <c r="N136" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O136" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="137" spans="1:15" x14ac:dyDescent="0.3">
@@ -10886,7 +11206,7 @@
         <v>3853</v>
       </c>
       <c r="K137" s="1" t="s">
-        <v>132</v>
+        <v>110</v>
       </c>
       <c r="L137" s="13">
         <v>46065</v>
@@ -10898,7 +11218,7 @@
         <v>1</v>
       </c>
       <c r="O137" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="138" spans="1:15" x14ac:dyDescent="0.3">
@@ -10906,7 +11226,7 @@
         <v>2026</v>
       </c>
       <c r="B138" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>14</v>
@@ -10933,10 +11253,10 @@
         <v>3853</v>
       </c>
       <c r="K138" s="1" t="s">
-        <v>133</v>
+        <v>111</v>
       </c>
       <c r="L138" s="13">
-        <v>46052</v>
+        <v>46084</v>
       </c>
       <c r="M138" s="1">
         <v>1</v>
@@ -10945,7 +11265,7 @@
         <v>1</v>
       </c>
       <c r="O138" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="139" spans="1:15" x14ac:dyDescent="0.3">
@@ -10953,7 +11273,7 @@
         <v>2026</v>
       </c>
       <c r="B139" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>14</v>
@@ -10980,19 +11300,19 @@
         <v>3853</v>
       </c>
       <c r="K139" s="1" t="s">
-        <v>184</v>
+        <v>126</v>
       </c>
       <c r="L139" s="13">
-        <v>46146</v>
+        <v>46062</v>
       </c>
       <c r="M139" s="1">
         <v>1</v>
       </c>
       <c r="N139" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O139" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="140" spans="1:15" x14ac:dyDescent="0.3">
@@ -11000,7 +11320,7 @@
         <v>2026</v>
       </c>
       <c r="B140" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>14</v>
@@ -11027,10 +11347,10 @@
         <v>3853</v>
       </c>
       <c r="K140" s="1" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="L140" s="13">
-        <v>46072</v>
+        <v>46087</v>
       </c>
       <c r="M140" s="1">
         <v>1</v>
@@ -11047,7 +11367,7 @@
         <v>2026</v>
       </c>
       <c r="B141" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>14</v>
@@ -11074,10 +11394,10 @@
         <v>3853</v>
       </c>
       <c r="K141" s="1" t="s">
-        <v>185</v>
+        <v>116</v>
       </c>
       <c r="L141" s="13">
-        <v>46143</v>
+        <v>46107</v>
       </c>
       <c r="M141" s="1">
         <v>1</v>
@@ -11121,10 +11441,10 @@
         <v>3853</v>
       </c>
       <c r="K142" s="1" t="s">
-        <v>53</v>
+        <v>117</v>
       </c>
       <c r="L142" s="13">
-        <v>46032</v>
+        <v>46024</v>
       </c>
       <c r="M142" s="1">
         <v>1</v>
@@ -11133,7 +11453,7 @@
         <v>1</v>
       </c>
       <c r="O142" s="1">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="143" spans="1:15" x14ac:dyDescent="0.3">
@@ -11141,7 +11461,7 @@
         <v>2026</v>
       </c>
       <c r="B143" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>14</v>
@@ -11168,19 +11488,19 @@
         <v>3853</v>
       </c>
       <c r="K143" s="1" t="s">
-        <v>172</v>
+        <v>118</v>
       </c>
       <c r="L143" s="13">
-        <v>46135</v>
+        <v>46035</v>
       </c>
       <c r="M143" s="1">
         <v>1</v>
       </c>
       <c r="N143" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O143" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="144" spans="1:15" x14ac:dyDescent="0.3">
@@ -11188,7 +11508,7 @@
         <v>2026</v>
       </c>
       <c r="B144" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>14</v>
@@ -11215,10 +11535,10 @@
         <v>3853</v>
       </c>
       <c r="K144" s="1" t="s">
-        <v>54</v>
+        <v>200</v>
       </c>
       <c r="L144" s="13">
-        <v>46075</v>
+        <v>46156</v>
       </c>
       <c r="M144" s="1">
         <v>1</v>
@@ -11235,7 +11555,7 @@
         <v>2026</v>
       </c>
       <c r="B145" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>14</v>
@@ -11262,19 +11582,19 @@
         <v>3853</v>
       </c>
       <c r="K145" s="1" t="s">
-        <v>128</v>
+        <v>184</v>
       </c>
       <c r="L145" s="13">
-        <v>46064</v>
+        <v>46146</v>
       </c>
       <c r="M145" s="1">
         <v>1</v>
       </c>
       <c r="N145" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O145" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146" spans="1:15" x14ac:dyDescent="0.3">
@@ -11309,10 +11629,10 @@
         <v>3853</v>
       </c>
       <c r="K146" s="1" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="L146" s="13">
-        <v>46058</v>
+        <v>46072</v>
       </c>
       <c r="M146" s="1">
         <v>1</v>
@@ -11322,6 +11642,758 @@
       </c>
       <c r="O146" s="1">
         <v>3</v>
+      </c>
+    </row>
+    <row r="147" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A147" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B147" s="1">
+        <v>1</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G147" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H147" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I147" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J147" s="1">
+        <v>3853</v>
+      </c>
+      <c r="K147" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="L147" s="13">
+        <v>46050</v>
+      </c>
+      <c r="M147" s="1">
+        <v>1</v>
+      </c>
+      <c r="N147" s="1">
+        <v>1</v>
+      </c>
+      <c r="O147" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="148" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A148" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B148" s="1">
+        <v>5</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E148" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F148" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G148" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H148" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I148" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J148" s="1">
+        <v>3853</v>
+      </c>
+      <c r="K148" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="L148" s="13">
+        <v>46157</v>
+      </c>
+      <c r="M148" s="1">
+        <v>1</v>
+      </c>
+      <c r="N148" s="1">
+        <v>0</v>
+      </c>
+      <c r="O148" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A149" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B149" s="1">
+        <v>1</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F149" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G149" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H149" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I149" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J149" s="1">
+        <v>3853</v>
+      </c>
+      <c r="K149" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="L149" s="13">
+        <v>46030</v>
+      </c>
+      <c r="M149" s="1">
+        <v>1</v>
+      </c>
+      <c r="N149" s="1">
+        <v>1</v>
+      </c>
+      <c r="O149" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="150" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A150" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B150" s="1">
+        <v>3</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E150" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F150" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G150" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H150" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I150" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J150" s="1">
+        <v>3853</v>
+      </c>
+      <c r="K150" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="L150" s="13">
+        <v>46096</v>
+      </c>
+      <c r="M150" s="1">
+        <v>1</v>
+      </c>
+      <c r="N150" s="1">
+        <v>1</v>
+      </c>
+      <c r="O150" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="151" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A151" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B151" s="1">
+        <v>2</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F151" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G151" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H151" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I151" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J151" s="1">
+        <v>3853</v>
+      </c>
+      <c r="K151" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="L151" s="13">
+        <v>46058</v>
+      </c>
+      <c r="M151" s="1">
+        <v>1</v>
+      </c>
+      <c r="N151" s="1">
+        <v>1</v>
+      </c>
+      <c r="O151" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="152" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A152" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B152" s="1">
+        <v>1</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E152" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F152" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G152" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H152" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I152" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J152" s="1">
+        <v>3853</v>
+      </c>
+      <c r="K152" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="L152" s="13">
+        <v>46034</v>
+      </c>
+      <c r="M152" s="1">
+        <v>1</v>
+      </c>
+      <c r="N152" s="1">
+        <v>1</v>
+      </c>
+      <c r="O152" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="153" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A153" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B153" s="1">
+        <v>2</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D153" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E153" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F153" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G153" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H153" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I153" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J153" s="1">
+        <v>3853</v>
+      </c>
+      <c r="K153" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="L153" s="13">
+        <v>46062</v>
+      </c>
+      <c r="M153" s="1">
+        <v>1</v>
+      </c>
+      <c r="N153" s="1">
+        <v>0</v>
+      </c>
+      <c r="O153" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A154" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B154" s="1">
+        <v>5</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F154" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G154" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H154" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I154" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J154" s="1">
+        <v>3853</v>
+      </c>
+      <c r="K154" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="L154" s="13">
+        <v>46157</v>
+      </c>
+      <c r="M154" s="1">
+        <v>1</v>
+      </c>
+      <c r="N154" s="1">
+        <v>1</v>
+      </c>
+      <c r="O154" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="155" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A155" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B155" s="1">
+        <v>2</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F155" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G155" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H155" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I155" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J155" s="1">
+        <v>3853</v>
+      </c>
+      <c r="K155" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="L155" s="13">
+        <v>46065</v>
+      </c>
+      <c r="M155" s="1">
+        <v>1</v>
+      </c>
+      <c r="N155" s="1">
+        <v>1</v>
+      </c>
+      <c r="O155" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="156" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A156" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B156" s="1">
+        <v>1</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E156" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F156" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G156" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H156" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I156" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J156" s="1">
+        <v>3853</v>
+      </c>
+      <c r="K156" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="L156" s="13">
+        <v>46052</v>
+      </c>
+      <c r="M156" s="1">
+        <v>1</v>
+      </c>
+      <c r="N156" s="1">
+        <v>1</v>
+      </c>
+      <c r="O156" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="157" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A157" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B157" s="1">
+        <v>4</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D157" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E157" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F157" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G157" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H157" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I157" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J157" s="1">
+        <v>3853</v>
+      </c>
+      <c r="K157" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="L157" s="13">
+        <v>46125</v>
+      </c>
+      <c r="M157" s="1">
+        <v>1</v>
+      </c>
+      <c r="N157" s="1">
+        <v>1</v>
+      </c>
+      <c r="O157" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="158" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A158" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B158" s="1">
+        <v>5</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D158" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E158" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F158" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G158" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H158" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I158" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J158" s="1">
+        <v>3853</v>
+      </c>
+      <c r="K158" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="L158" s="13">
+        <v>46143</v>
+      </c>
+      <c r="M158" s="1">
+        <v>1</v>
+      </c>
+      <c r="N158" s="1">
+        <v>0</v>
+      </c>
+      <c r="O158" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A159" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B159" s="1">
+        <v>1</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E159" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F159" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G159" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H159" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I159" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J159" s="1">
+        <v>3853</v>
+      </c>
+      <c r="K159" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="L159" s="13">
+        <v>46032</v>
+      </c>
+      <c r="M159" s="1">
+        <v>1</v>
+      </c>
+      <c r="N159" s="1">
+        <v>1</v>
+      </c>
+      <c r="O159" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="160" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A160" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B160" s="1">
+        <v>4</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E160" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F160" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G160" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H160" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I160" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J160" s="1">
+        <v>3853</v>
+      </c>
+      <c r="K160" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="L160" s="13">
+        <v>46135</v>
+      </c>
+      <c r="M160" s="1">
+        <v>1</v>
+      </c>
+      <c r="N160" s="1">
+        <v>0</v>
+      </c>
+      <c r="O160" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A161" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B161" s="1">
+        <v>2</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E161" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F161" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G161" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H161" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I161" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J161" s="1">
+        <v>3853</v>
+      </c>
+      <c r="K161" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L161" s="13">
+        <v>46075</v>
+      </c>
+      <c r="M161" s="1">
+        <v>1</v>
+      </c>
+      <c r="N161" s="1">
+        <v>0</v>
+      </c>
+      <c r="O161" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A162" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B162" s="1">
+        <v>2</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E162" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F162" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G162" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H162" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I162" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J162" s="1">
+        <v>3853</v>
+      </c>
+      <c r="K162" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="L162" s="13">
+        <v>46064</v>
+      </c>
+      <c r="M162" s="1">
+        <v>1</v>
+      </c>
+      <c r="N162" s="1">
+        <v>1</v>
+      </c>
+      <c r="O162" s="1">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
